--- a/parameters/neurons_parameters.xlsx
+++ b/parameters/neurons_parameters.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -680,37 +680,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -784,7 +784,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.62"/>
@@ -2689,8 +2689,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2701,7 +2701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U131"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.77"/>
@@ -2861,7 +2861,7 @@
         <v>160000</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>20</v>
@@ -2985,7 +2985,7 @@
         <v>160000</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
@@ -3047,7 +3047,7 @@
         <v>160000</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
@@ -3109,7 +3109,7 @@
         <v>160000</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
@@ -3171,7 +3171,7 @@
         <v>160000</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>20</v>
@@ -3233,7 +3233,7 @@
         <v>160000</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
@@ -3295,7 +3295,7 @@
         <v>160000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
@@ -3357,7 +3357,7 @@
         <v>160000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>20</v>
@@ -3419,7 +3419,7 @@
         <v>160000</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
@@ -3481,7 +3481,7 @@
         <v>160000</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>20</v>
@@ -3543,7 +3543,7 @@
         <v>160000</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>20</v>
@@ -3605,7 +3605,7 @@
         <v>160000</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>20</v>
@@ -3667,7 +3667,7 @@
         <v>160000</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>20</v>
@@ -3729,7 +3729,7 @@
         <v>160000</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>20</v>
@@ -3791,7 +3791,7 @@
         <v>160000</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>20</v>
@@ -3853,7 +3853,7 @@
         <v>160000</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>20</v>
@@ -3915,7 +3915,7 @@
         <v>160000</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>20</v>
@@ -3977,7 +3977,7 @@
         <v>160000</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>20</v>
@@ -4039,7 +4039,7 @@
         <v>160000</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>20</v>
@@ -4163,7 +4163,7 @@
         <v>160000</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>24</v>
@@ -4225,7 +4225,7 @@
         <v>160000</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>24</v>
@@ -4287,7 +4287,7 @@
         <v>160000</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>24</v>
@@ -4349,7 +4349,7 @@
         <v>160000</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>24</v>
@@ -4473,7 +4473,7 @@
         <v>160000</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>24</v>
@@ -4535,7 +4535,7 @@
         <v>160000</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>24</v>
@@ -4597,7 +4597,7 @@
         <v>160000</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>24</v>
@@ -4659,7 +4659,7 @@
         <v>160000</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>24</v>
@@ -4721,7 +4721,7 @@
         <v>160000</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>24</v>
@@ -4783,7 +4783,7 @@
         <v>160000</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>24</v>
@@ -4845,7 +4845,7 @@
         <v>160000</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>24</v>
@@ -4907,7 +4907,7 @@
         <v>160000</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>24</v>
@@ -4969,7 +4969,7 @@
         <v>160000</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>24</v>
@@ -5031,7 +5031,7 @@
         <v>160000</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>24</v>
@@ -5093,7 +5093,7 @@
         <v>160000</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>24</v>
@@ -5155,7 +5155,7 @@
         <v>160000</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>24</v>
@@ -5217,7 +5217,7 @@
         <v>160000</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>24</v>
@@ -5279,7 +5279,7 @@
         <v>160000</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>24</v>
@@ -5341,7 +5341,7 @@
         <v>160000</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>24</v>
@@ -5391,7 +5391,7 @@
         <v>26</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>1</v>
@@ -5446,7 +5446,7 @@
         <v>29</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
@@ -5490,7 +5490,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>33</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>1</v>
@@ -5589,7 +5589,7 @@
         <v>37</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         <v>39</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>1</v>
@@ -5688,7 +5688,7 @@
         <v>43</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>1</v>
@@ -5742,7 +5742,7 @@
         <v>45</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
         <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>53</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
         <v>55</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>57</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>59</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>61</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
         <v>63</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>1</v>
@@ -6126,7 +6126,7 @@
         <v>66</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>0</v>
@@ -6176,7 +6176,7 @@
         <v>69</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>1</v>
@@ -6231,7 +6231,7 @@
         <v>72</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0</v>
@@ -6276,7 +6276,7 @@
         <v>74</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>78</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         <v>80</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>82</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
         <v>84</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -6543,7 +6543,7 @@
         <v>86</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>88</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>1</v>
@@ -6642,7 +6642,7 @@
         <v>92</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
@@ -6687,7 +6687,7 @@
         <v>94</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
         <v>96</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>1</v>
@@ -6786,7 +6786,7 @@
         <v>100</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>0</v>
@@ -6831,7 +6831,7 @@
         <v>102</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>0</v>
@@ -6876,7 +6876,7 @@
         <v>104</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1</v>
@@ -6930,7 +6930,7 @@
         <v>106</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D76" s="4" t="n">
         <v>1</v>
@@ -6987,7 +6987,7 @@
         <v>110</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>112</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>0</v>
@@ -7076,7 +7076,7 @@
         <v>114</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>1</v>
@@ -7130,7 +7130,7 @@
         <v>117</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>0</v>
@@ -9407,8 +9407,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9419,7 +9419,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="11.62"/>
@@ -10900,8 +10900,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10912,7 +10912,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="26.64"/>
@@ -12722,8 +12722,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Страница &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>